--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/FillAtReservedPosition-SavePredefinedValues-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/FillAtReservedPosition-SavePredefinedValues-Output.xlsx
@@ -400,22 +400,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{CCCEE2C1-16B7-4D3F-847E-180D21B7A375}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:sheetData>
     <x:row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>